--- a/dataset/review result/Python/正确_检查22个.xlsx
+++ b/dataset/review result/Python/正确_检查22个.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oywy2\Desktop\增补数据校验\增补数据校验\【增补review数据集】\Python\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\LLM-CMT\dataset\review result\Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80AF01B4-5034-41B3-9BA0-CEE0F34FF3FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC3C63F6-6FD1-4E96-AA34-B496E08AEB6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-690" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="-35550" yWindow="2280" windowWidth="28635" windowHeight="18585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -53,9 +53,6 @@
     <t>569API.py</t>
   </si>
   <si>
-    <t>AES is no longer secure.</t>
-  </si>
-  <si>
     <t>373cryptostore.py</t>
   </si>
   <si>
@@ -117,6 +114,10 @@
   </si>
   <si>
     <t>400multicast.py</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ECB mode is not secure.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -136,6 +137,7 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -509,21 +511,21 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="3">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="B4" s="3">
-        <v>0</v>
-      </c>
-      <c r="C4" s="3">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -534,7 +536,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -545,7 +547,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -556,7 +558,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -567,7 +569,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -578,21 +580,21 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="3">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B10" s="3">
-        <v>0</v>
-      </c>
-      <c r="C10" s="3">
-        <v>1</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" s="3">
         <v>1</v>
@@ -603,7 +605,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" s="3">
         <v>1</v>
@@ -614,7 +616,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" s="3">
         <v>1</v>
@@ -625,7 +627,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" s="3">
         <v>1</v>
@@ -636,7 +638,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" s="3">
         <v>1</v>
@@ -647,7 +649,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" s="3">
         <v>1</v>
@@ -658,7 +660,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" s="3">
         <v>1</v>
@@ -669,7 +671,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" s="3">
         <v>1</v>
@@ -680,7 +682,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" s="1">
         <v>1</v>
@@ -691,7 +693,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" s="1">
         <v>1</v>
@@ -702,7 +704,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" s="1">
         <v>1</v>
@@ -713,7 +715,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" s="1">
         <v>1</v>
@@ -724,7 +726,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" s="1">
         <v>1</v>
